--- a/Data/GPS/Info spectral measure_biomass core_BdA 2026.xlsx
+++ b/Data/GPS/Info spectral measure_biomass core_BdA 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://joinnioz-my.sharepoint.com/personal/jim_de_fouw_nioz_nl/Documents/Documenten/1_Research/1_NIOZ/BdA 2025/1_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon\Nextcloud\Project\Mauritania\Science\Arguin - FieldWork Data Processing\Data\GPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{6ED80282-4AB6-4C2D-9F21-FC7EC8AD4E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4147640-E852-4141-BB1A-04CF9D48DCAA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C72B1BC-DF95-4EC9-B241-3EB47A848D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B06B580A-CD3D-4BAA-8B21-F753C19C794D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B06B580A-CD3D-4BAA-8B21-F753C19C794D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="272">
   <si>
     <t>station</t>
   </si>
@@ -999,7 +999,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1316,14 +1316,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F919BFD3-93A9-47ED-BB17-746998AE3C2E}">
   <dimension ref="A1:K131"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.06640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>-16.313044000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>-16.313427000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>-16.313679</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>-16.313692</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>-16.313727</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>-16.314359</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>-16.314457000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>-16.314544999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>-16.314571999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>-16.314478000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>-16.314516000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>-16.314572999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>-16.314695</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>-16.315055999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>-16.315086000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>-16.315237</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>-16.315111999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>-16.314893000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>-16.313925999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>-16.313889</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>5.9774929999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>5.9769550000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>63</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>5.9772939999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>65</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>5.9772309999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>5.9927289999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>5.992</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>71</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>5.9918889999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>73</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>5.9911960000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>75</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>5.9910620000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>-16.281448999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>-16.281472000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>81</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>-16.281461</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>83</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>-16.281452000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>85</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>-16.281514999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>-16.281535000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>89</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>-16.281513</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>-16.281535000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>93</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>-16.281513</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -2603,7 +2603,7 @@
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -2632,7 +2632,7 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -2661,7 +2661,7 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>99</v>
       </c>
@@ -2690,7 +2690,7 @@
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>100</v>
       </c>
@@ -2719,7 +2719,7 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>101</v>
       </c>
@@ -2748,7 +2748,7 @@
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>102</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>-16.281448999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>-16.281472000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>-16.281452000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>-16.281461</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>-16.281514999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>-16.281535000000002</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>-16.281513</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>-16.282052</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>120</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>-16.281798999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>122</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>-16.281838</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>124</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>-16.281753999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>126</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>-16.281856000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>128</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>-16.282342</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>130</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>-16.282402999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>132</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>-16.282477</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>134</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>-16.282495999999998</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>136</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>-16.282468000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>138</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>-16.283480000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>-16.283462</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>-16.284215</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>146</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>-16.284192999999998</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>148</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>-16.284199999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>150</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>-16.398688</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>153</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>-16.398688</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>154</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>-16.398688</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>155</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>-16.398752000000002</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>156</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>-16.398864</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>-16.399487000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>159</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>-16.399487000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>160</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>-16.399487000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>161</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>-16.380110999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>163</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>-16.380179999999999</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>165</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>-16.380254000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>167</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>-16.380144999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>169</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>-16.380016999999999</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>171</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>-16.379705000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>173</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>176</v>
       </c>
@@ -3979,7 +3979,7 @@
         <v>-16.379840000000002</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>178</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>-16.379615000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>180</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>-16.381028000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>182</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>-16.381343999999999</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>184</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>-16.381346000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>186</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>-16.381409999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>188</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>-16.381440000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>190</v>
       </c>
@@ -4206,7 +4206,7 @@
         <v>-16.283103000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>193</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>-16.283683</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>195</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>-16.284056</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>197</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>-16.282484</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>199</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>-16.282426000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>201</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>-16.282558999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>203</v>
       </c>
@@ -4413,7 +4413,7 @@
         <v>-16.282478999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>205</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>-16.282328</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>208</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>-16.282328</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>209</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>-16.282328</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>210</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>-16.282328</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>211</v>
       </c>
@@ -4573,7 +4573,7 @@
         <v>-16.282679999999999</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>213</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>-16.282679999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>214</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>-16.282679999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>215</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>216</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>217</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>218</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>219</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>220</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>221</v>
       </c>
@@ -4833,14 +4833,14 @@
       <c r="I110" t="s">
         <v>224</v>
       </c>
-      <c r="J110" t="s">
-        <v>49</v>
-      </c>
-      <c r="K110" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J110">
+        <v>19.883937</v>
+      </c>
+      <c r="K110">
+        <v>-16.294369</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>225</v>
       </c>
@@ -4862,14 +4862,14 @@
       <c r="I111" t="s">
         <v>224</v>
       </c>
-      <c r="J111" t="s">
-        <v>49</v>
-      </c>
-      <c r="K111" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J111">
+        <v>19.883815999999999</v>
+      </c>
+      <c r="K111">
+        <v>-16.294463</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>226</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>-16.499679</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>229</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>-16.500781</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>232</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>-16.504162000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>235</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>-16.504517</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>238</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>-16.508523</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>241</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>-16.502755000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>243</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>-16.506917000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>245</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>-16.506903000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>247</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>-16.507075</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>249</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>-16.507142000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>251</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>-16.507878000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>253</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>-16.508063</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>255</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>-16.508149</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>257</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>-16.302130999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>260</v>
       </c>
@@ -5373,7 +5373,7 @@
         <v>-16.301926000000002</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>262</v>
       </c>
@@ -5408,7 +5408,7 @@
         <v>-16.301793</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>264</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>-16.301748</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>266</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>-16.301705999999999</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>268</v>
       </c>
@@ -5513,7 +5513,7 @@
         <v>-16.301518999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>270</v>
       </c>
@@ -5545,6 +5545,7 @@
   </sheetData>
   <autoFilter ref="A1:K131" xr:uid="{F919BFD3-93A9-47ED-BB17-746998AE3C2E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Data/GPS/Info spectral measure_biomass core_BdA 2026.xlsx
+++ b/Data/GPS/Info spectral measure_biomass core_BdA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon\Nextcloud\Project\Mauritania\Science\Arguin - FieldWork Data Processing\Data\GPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C72B1BC-DF95-4EC9-B241-3EB47A848D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1EAD8C-95DC-4529-939C-AD015388C2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B06B580A-CD3D-4BAA-8B21-F753C19C794D}"/>
   </bookViews>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="276">
   <si>
     <t>station</t>
   </si>
@@ -913,6 +913,18 @@
   </si>
   <si>
     <t>0511</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>Coastal</t>
+  </si>
+  <si>
+    <t>Transitional</t>
+  </si>
+  <si>
+    <t>Off-shore</t>
   </si>
 </sst>
 </file>
@@ -1315,15 +1327,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F919BFD3-93A9-47ED-BB17-746998AE3C2E}">
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="5" max="5" width="9.06640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="14.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1357,8 +1369,11 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L1" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1404,11 @@
       <c r="K2">
         <v>-16.313044000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1421,8 +1439,11 @@
       <c r="K3">
         <v>-16.313427000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1453,8 +1474,11 @@
       <c r="K4">
         <v>-16.313679</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1485,8 +1509,11 @@
       <c r="K5">
         <v>-16.313692</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1517,8 +1544,11 @@
       <c r="K6">
         <v>-16.313727</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1549,8 +1579,11 @@
       <c r="K7">
         <v>-16.314359</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1581,8 +1614,11 @@
       <c r="K8">
         <v>-16.314457000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1613,8 +1649,11 @@
       <c r="K9">
         <v>-16.314544999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1645,8 +1684,11 @@
       <c r="K10">
         <v>-16.314571999999998</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1677,8 +1719,11 @@
       <c r="K11">
         <v>-16.314478000000001</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L11" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1709,8 +1754,11 @@
       <c r="K12">
         <v>-16.314516000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1741,8 +1789,11 @@
       <c r="K13">
         <v>-16.314572999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L13" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -1773,8 +1824,11 @@
       <c r="K14">
         <v>-16.314695</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L14" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1805,8 +1859,11 @@
       <c r="K15">
         <v>-16.315055999999998</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L15" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1837,8 +1894,11 @@
       <c r="K16">
         <v>-16.315086000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L16" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1869,8 +1929,11 @@
       <c r="K17">
         <v>-16.315237</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L17" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1901,8 +1964,11 @@
       <c r="K18">
         <v>-16.315111999999999</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L18" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1933,8 +1999,11 @@
       <c r="K19">
         <v>-16.314893000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L19" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1965,8 +2034,11 @@
       <c r="K20">
         <v>-16.313925999999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L20" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1997,8 +2069,11 @@
       <c r="K21">
         <v>-16.313889</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L21" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -2029,8 +2104,11 @@
       <c r="K22">
         <v>5.9774929999999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L22" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -2061,8 +2139,11 @@
       <c r="K23">
         <v>5.9769550000000002</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L23" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>63</v>
       </c>
@@ -2093,8 +2174,11 @@
       <c r="K24">
         <v>5.9772939999999997</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L24" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>65</v>
       </c>
@@ -2125,8 +2209,11 @@
       <c r="K25">
         <v>5.9772309999999997</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L25" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -2157,8 +2244,11 @@
       <c r="K26">
         <v>5.9927289999999998</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L26" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -2189,8 +2279,11 @@
       <c r="K27">
         <v>5.992</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L27" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>71</v>
       </c>
@@ -2221,8 +2314,11 @@
       <c r="K28">
         <v>5.9918889999999996</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L28" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>73</v>
       </c>
@@ -2253,8 +2349,11 @@
       <c r="K29">
         <v>5.9911960000000004</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L29" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>75</v>
       </c>
@@ -2285,8 +2384,11 @@
       <c r="K30">
         <v>5.9910620000000003</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L30" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -2317,8 +2419,11 @@
       <c r="K31">
         <v>-16.281448999999999</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L31" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -2349,8 +2454,11 @@
       <c r="K32">
         <v>-16.281472000000001</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L32" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>81</v>
       </c>
@@ -2381,8 +2489,11 @@
       <c r="K33">
         <v>-16.281461</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L33" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>83</v>
       </c>
@@ -2413,8 +2524,11 @@
       <c r="K34">
         <v>-16.281452000000002</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L34" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>85</v>
       </c>
@@ -2445,8 +2559,11 @@
       <c r="K35">
         <v>-16.281514999999999</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L35" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -2477,8 +2594,11 @@
       <c r="K36">
         <v>-16.281535000000002</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L36" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>89</v>
       </c>
@@ -2509,8 +2629,11 @@
       <c r="K37">
         <v>-16.281513</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L37" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -2541,8 +2664,11 @@
       <c r="K38">
         <v>-16.281535000000002</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L38" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>93</v>
       </c>
@@ -2573,8 +2699,11 @@
       <c r="K39">
         <v>-16.281513</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L39" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -2602,8 +2731,11 @@
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L40" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -2631,8 +2763,11 @@
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L41" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -2660,8 +2795,11 @@
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L42" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>99</v>
       </c>
@@ -2689,8 +2827,11 @@
       </c>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L43" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>100</v>
       </c>
@@ -2718,8 +2859,11 @@
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L44" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>101</v>
       </c>
@@ -2747,8 +2891,11 @@
       </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L45" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>102</v>
       </c>
@@ -2779,8 +2926,11 @@
       <c r="K46">
         <v>-16.281448999999999</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L46" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2811,8 +2961,11 @@
       <c r="K47">
         <v>-16.281472000000001</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L47" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2843,8 +2996,11 @@
       <c r="K48">
         <v>-16.281452000000002</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L48" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2875,8 +3031,11 @@
       <c r="K49">
         <v>-16.281461</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L49" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2907,8 +3066,11 @@
       <c r="K50">
         <v>-16.281514999999999</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L50" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2939,8 +3101,11 @@
       <c r="K51">
         <v>-16.281535000000002</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L51" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2971,8 +3136,11 @@
       <c r="K52">
         <v>-16.281513</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L52" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -3003,8 +3171,11 @@
       <c r="K53">
         <v>-16.282052</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L53" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>120</v>
       </c>
@@ -3035,8 +3206,11 @@
       <c r="K54">
         <v>-16.281798999999999</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L54" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>122</v>
       </c>
@@ -3067,8 +3241,11 @@
       <c r="K55">
         <v>-16.281838</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L55" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>124</v>
       </c>
@@ -3099,8 +3276,11 @@
       <c r="K56">
         <v>-16.281753999999999</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L56" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>126</v>
       </c>
@@ -3131,8 +3311,11 @@
       <c r="K57">
         <v>-16.281856000000001</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L57" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>128</v>
       </c>
@@ -3163,8 +3346,11 @@
       <c r="K58">
         <v>-16.282342</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L58" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>130</v>
       </c>
@@ -3195,8 +3381,11 @@
       <c r="K59">
         <v>-16.282402999999999</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L59" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>132</v>
       </c>
@@ -3227,8 +3416,11 @@
       <c r="K60">
         <v>-16.282477</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L60" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>134</v>
       </c>
@@ -3259,8 +3451,11 @@
       <c r="K61">
         <v>-16.282495999999998</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L61" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>136</v>
       </c>
@@ -3291,8 +3486,11 @@
       <c r="K62">
         <v>-16.282468000000001</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L62" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>138</v>
       </c>
@@ -3323,8 +3521,11 @@
       <c r="K63">
         <v>-16.283480000000001</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L63" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -3355,8 +3556,11 @@
       <c r="K64">
         <v>-16.283462</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L64" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -3387,8 +3591,11 @@
       <c r="K65">
         <v>-16.284215</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L65" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>146</v>
       </c>
@@ -3419,8 +3626,11 @@
       <c r="K66">
         <v>-16.284192999999998</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L66" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>148</v>
       </c>
@@ -3451,8 +3661,11 @@
       <c r="K67">
         <v>-16.284199999999998</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L67" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>150</v>
       </c>
@@ -3483,8 +3696,11 @@
       <c r="K68">
         <v>-16.398688</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L68" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>153</v>
       </c>
@@ -3515,8 +3731,11 @@
       <c r="K69">
         <v>-16.398688</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L69" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>154</v>
       </c>
@@ -3547,8 +3766,11 @@
       <c r="K70">
         <v>-16.398688</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L70" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>155</v>
       </c>
@@ -3579,8 +3801,11 @@
       <c r="K71">
         <v>-16.398752000000002</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L71" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>156</v>
       </c>
@@ -3611,8 +3836,11 @@
       <c r="K72">
         <v>-16.398864</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L72" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -3643,8 +3871,11 @@
       <c r="K73">
         <v>-16.399487000000001</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L73" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>159</v>
       </c>
@@ -3675,8 +3906,11 @@
       <c r="K74">
         <v>-16.399487000000001</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L74" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>160</v>
       </c>
@@ -3707,8 +3941,11 @@
       <c r="K75">
         <v>-16.399487000000001</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L75" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>161</v>
       </c>
@@ -3742,8 +3979,11 @@
       <c r="K76">
         <v>-16.380110999999999</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L76" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>163</v>
       </c>
@@ -3777,8 +4017,11 @@
       <c r="K77">
         <v>-16.380179999999999</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L77" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>165</v>
       </c>
@@ -3812,8 +4055,11 @@
       <c r="K78">
         <v>-16.380254000000001</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L78" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>167</v>
       </c>
@@ -3847,8 +4093,11 @@
       <c r="K79">
         <v>-16.380144999999999</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L79" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>169</v>
       </c>
@@ -3882,8 +4131,11 @@
       <c r="K80">
         <v>-16.380016999999999</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L80" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>171</v>
       </c>
@@ -3917,8 +4169,11 @@
       <c r="K81">
         <v>-16.379705000000001</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L81" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>173</v>
       </c>
@@ -3946,8 +4201,11 @@
       <c r="K82" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L82" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>176</v>
       </c>
@@ -3978,8 +4236,11 @@
       <c r="K83">
         <v>-16.379840000000002</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L83" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>178</v>
       </c>
@@ -4010,8 +4271,11 @@
       <c r="K84">
         <v>-16.379615000000001</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L84" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>180</v>
       </c>
@@ -4042,8 +4306,11 @@
       <c r="K85">
         <v>-16.381028000000001</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L85" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>182</v>
       </c>
@@ -4074,8 +4341,11 @@
       <c r="K86">
         <v>-16.381343999999999</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L86" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>184</v>
       </c>
@@ -4106,8 +4376,11 @@
       <c r="K87">
         <v>-16.381346000000001</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L87" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>186</v>
       </c>
@@ -4138,8 +4411,11 @@
       <c r="K88">
         <v>-16.381409999999999</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L88" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>188</v>
       </c>
@@ -4170,8 +4446,11 @@
       <c r="K89">
         <v>-16.381440000000001</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L89" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>190</v>
       </c>
@@ -4205,8 +4484,11 @@
       <c r="K90">
         <v>-16.283103000000001</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L90" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>193</v>
       </c>
@@ -4240,8 +4522,11 @@
       <c r="K91">
         <v>-16.283683</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L91" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>195</v>
       </c>
@@ -4275,8 +4560,11 @@
       <c r="K92">
         <v>-16.284056</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L92" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>197</v>
       </c>
@@ -4310,8 +4598,11 @@
       <c r="K93">
         <v>-16.282484</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L93" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>199</v>
       </c>
@@ -4342,8 +4633,11 @@
       <c r="K94">
         <v>-16.282426000000001</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L94" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>201</v>
       </c>
@@ -4377,8 +4671,11 @@
       <c r="K95">
         <v>-16.282558999999999</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L95" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>203</v>
       </c>
@@ -4412,8 +4709,11 @@
       <c r="K96">
         <v>-16.282478999999999</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L96" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>205</v>
       </c>
@@ -4444,8 +4744,11 @@
       <c r="K97">
         <v>-16.282328</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L97" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>208</v>
       </c>
@@ -4476,8 +4779,11 @@
       <c r="K98">
         <v>-16.282328</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L98" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>209</v>
       </c>
@@ -4508,8 +4814,11 @@
       <c r="K99">
         <v>-16.282328</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L99" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>210</v>
       </c>
@@ -4540,8 +4849,11 @@
       <c r="K100">
         <v>-16.282328</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L100" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>211</v>
       </c>
@@ -4572,8 +4884,11 @@
       <c r="K101">
         <v>-16.282679999999999</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L101" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>213</v>
       </c>
@@ -4604,8 +4919,11 @@
       <c r="K102">
         <v>-16.282679999999999</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L102" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>214</v>
       </c>
@@ -4636,8 +4954,11 @@
       <c r="K103">
         <v>-16.282679999999999</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L103" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>215</v>
       </c>
@@ -4665,8 +4986,11 @@
       <c r="K104" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L104" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>216</v>
       </c>
@@ -4694,8 +5018,11 @@
       <c r="K105" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L105" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>217</v>
       </c>
@@ -4723,8 +5050,11 @@
       <c r="K106" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L106" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>218</v>
       </c>
@@ -4752,8 +5082,11 @@
       <c r="K107" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L107" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>219</v>
       </c>
@@ -4781,8 +5114,11 @@
       <c r="K108" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L108" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>220</v>
       </c>
@@ -4810,8 +5146,11 @@
       <c r="K109" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L109" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>221</v>
       </c>
@@ -4839,8 +5178,11 @@
       <c r="K110">
         <v>-16.294369</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L110" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>225</v>
       </c>
@@ -4868,8 +5210,11 @@
       <c r="K111">
         <v>-16.294463</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L111" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>226</v>
       </c>
@@ -4900,8 +5245,11 @@
       <c r="K112">
         <v>-16.499679</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L112" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>229</v>
       </c>
@@ -4932,8 +5280,11 @@
       <c r="K113">
         <v>-16.500781</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L113" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>232</v>
       </c>
@@ -4964,8 +5315,11 @@
       <c r="K114">
         <v>-16.504162000000001</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L114" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>235</v>
       </c>
@@ -4996,8 +5350,11 @@
       <c r="K115">
         <v>-16.504517</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L115" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>238</v>
       </c>
@@ -5028,8 +5385,11 @@
       <c r="K116">
         <v>-16.508523</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L116" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>241</v>
       </c>
@@ -5060,8 +5420,11 @@
       <c r="K117">
         <v>-16.502755000000001</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L117" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>243</v>
       </c>
@@ -5095,8 +5458,11 @@
       <c r="K118">
         <v>-16.506917000000001</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L118" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>245</v>
       </c>
@@ -5130,8 +5496,11 @@
       <c r="K119">
         <v>-16.506903000000001</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L119" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>247</v>
       </c>
@@ -5165,8 +5534,11 @@
       <c r="K120">
         <v>-16.507075</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L120" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>249</v>
       </c>
@@ -5200,8 +5572,11 @@
       <c r="K121">
         <v>-16.507142000000002</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L121" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>251</v>
       </c>
@@ -5235,8 +5610,11 @@
       <c r="K122">
         <v>-16.507878000000002</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L122" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>253</v>
       </c>
@@ -5270,8 +5648,11 @@
       <c r="K123">
         <v>-16.508063</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L123" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>255</v>
       </c>
@@ -5302,8 +5683,11 @@
       <c r="K124">
         <v>-16.508149</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L124" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>257</v>
       </c>
@@ -5337,8 +5721,11 @@
       <c r="K125">
         <v>-16.302130999999999</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L125" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>260</v>
       </c>
@@ -5372,8 +5759,11 @@
       <c r="K126">
         <v>-16.301926000000002</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L126" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>262</v>
       </c>
@@ -5407,8 +5797,11 @@
       <c r="K127">
         <v>-16.301793</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L127" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>264</v>
       </c>
@@ -5442,8 +5835,11 @@
       <c r="K128">
         <v>-16.301748</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L128" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>266</v>
       </c>
@@ -5477,8 +5873,11 @@
       <c r="K129">
         <v>-16.301705999999999</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L129" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>268</v>
       </c>
@@ -5512,8 +5911,11 @@
       <c r="K130">
         <v>-16.301518999999999</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L130" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>270</v>
       </c>
@@ -5540,6 +5942,9 @@
       </c>
       <c r="K131">
         <v>-16.302872000000001</v>
+      </c>
+      <c r="L131" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
